--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrAssetConfigTransfer.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrAssetConfigTransfer.xlsx
@@ -42,7 +42,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>剩余期限</t>
+    <t>剩余期限(天)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrAssetConfigTransfer.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrAssetConfigTransfer.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace_tg\branches_tzjy_3.0_deploy\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -42,7 +42,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>剩余期限(天)</t>
+    <t>剩余期限</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
